--- a/AAII_Financials/Quarterly/LITE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LITE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>LITE</t>
   </si>
@@ -656,538 +656,551 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46018</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44562</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44191</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1006300</v>
+      </c>
+      <c r="E8" s="3">
         <v>808400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>665500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>533800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>480700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>425200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>402200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>336900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>308300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>366500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>366800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>317600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>370800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>383400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>506000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>506800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>422100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>395400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>446700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>448400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>392100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>419500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>478800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>452400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>368100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>402800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>457800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>449900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>404600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>432900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>373700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>354100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>301100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>298800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>404600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>243200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>222700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>255800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>265000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>258100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>509800</v>
+      </c>
+      <c r="E9" s="3">
         <v>432100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>405800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>332800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>301500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>283700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>281200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>236500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>234900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>279800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>277900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>222900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>238600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>252700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>339800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>305600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>240400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>228200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>239200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>216200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>229300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>234500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>249200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>246700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>232400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>245100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>268700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>282200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>317800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>344600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>248900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>228100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>205600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>201800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>233500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>174700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>155400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>173700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>178000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>176400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>496500</v>
+      </c>
+      <c r="E10" s="3">
         <v>376300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>259700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>201000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>179200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>141500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>121000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>100400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>73400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>86700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>88900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>94700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>132200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>130700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>166200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>201200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>181700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>167200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>207500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>232200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>162800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>185000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>229600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>205700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>135700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>157700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>189100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>167700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>86800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>88300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>124800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>126000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>95500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>97000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>171100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>68500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>67300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>82100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>87000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>81700</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1230,130 +1243,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>104400</v>
+      </c>
+      <c r="E12" s="3">
         <v>90600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>80100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>81400</v>
       </c>
-      <c r="G12" s="3">
-        <v>76800</v>
-      </c>
       <c r="H12" s="3">
+        <v>79500</v>
+      </c>
+      <c r="I12" s="3">
         <v>75900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>74200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>74300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>73200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>77200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>78300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>73500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>72500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>73900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>75800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>72700</v>
-      </c>
-      <c r="S12" s="3">
-        <v>56700</v>
       </c>
       <c r="T12" s="3">
         <v>56700</v>
       </c>
       <c r="U12" s="3">
+        <v>56700</v>
+      </c>
+      <c r="V12" s="3">
         <v>53200</v>
-      </c>
-      <c r="V12" s="3">
-        <v>54100</v>
       </c>
       <c r="W12" s="3">
         <v>54100</v>
       </c>
       <c r="X12" s="3">
+        <v>54100</v>
+      </c>
+      <c r="Y12" s="3">
         <v>57200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>52800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>50400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>49000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>48700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>51000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>49900</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>49500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>57700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>42800</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>34600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>38500</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>38200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>43800</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>36300</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>35400</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>37300</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>38700</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>36900</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1474,225 +1491,231 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>7758600</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-20400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8300</v>
       </c>
-      <c r="G14" s="3">
-        <v>7900</v>
-      </c>
       <c r="H14" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I14" s="3">
         <v>-27700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>36800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>24100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>18200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>37300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>13100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9300</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-1100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-204600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>200</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>4900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>51800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>7800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>1300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>4500</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>2900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>2000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>3100</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>4000</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E15" s="3">
         <v>19300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>19600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>19500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>19300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>21400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>22500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>22100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>22300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>21500</v>
-      </c>
-      <c r="N15" s="3">
-        <v>18000</v>
       </c>
       <c r="O15" s="3">
         <v>18000</v>
       </c>
       <c r="P15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>18700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>11300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>9300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>5600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>5800</v>
-      </c>
-      <c r="U15" s="3">
-        <v>5600</v>
       </c>
       <c r="V15" s="3">
         <v>5600</v>
       </c>
       <c r="W15" s="3">
-        <v>6200</v>
+        <v>5600</v>
       </c>
       <c r="X15" s="3">
         <v>6200</v>
       </c>
       <c r="Y15" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Z15" s="3">
         <v>5900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>5700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>6200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>6100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>6200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>6300</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>3600</v>
       </c>
       <c r="AF15" s="3">
         <v>3600</v>
       </c>
       <c r="AG15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AH15" s="3">
         <v>800</v>
-      </c>
-      <c r="AH15" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AI15" s="3" t="s">
         <v>17</v>
@@ -1700,17 +1723,17 @@
       <c r="AJ15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AK15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="3" t="s">
+      <c r="AK15" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>0</v>
       </c>
       <c r="AM15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AN15" s="3">
-        <v>0</v>
+      <c r="AN15" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AO15" s="3">
         <v>0</v>
@@ -1718,8 +1741,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1759,252 +1785,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>725000</v>
+      </c>
+      <c r="E17" s="3">
         <v>632400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>594100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>518800</v>
       </c>
-      <c r="G17" s="3">
-        <v>481200</v>
-      </c>
       <c r="H17" s="3">
+        <v>483900</v>
+      </c>
+      <c r="I17" s="3">
         <v>490600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>453100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>409600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>404900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>457000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>453800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>385000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>388400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>421700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>527900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>493300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>366700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>348600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>361500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>332500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>346300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>152600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>363500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>353400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>341100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>360300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>383000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>390100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>418400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>509300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>362200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>297000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>280200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>273300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>313800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>240500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>218800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>242200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>251700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>241300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>281300</v>
+      </c>
+      <c r="E18" s="3">
         <v>176000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>71400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-500</v>
-      </c>
       <c r="H18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-65400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-50900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-72700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-96600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-90500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-87000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-67400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-17600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-38300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>55400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>46800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>85200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>115900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>45800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>266900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>115300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>99000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>27000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>42500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>74800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>59800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-13800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-76400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>11500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>57100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>25500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>90800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>13600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>13300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2047,350 +2080,357 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>13800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>21700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>14700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>11400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-18200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>9300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>5200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-31500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-58000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>4600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-22500</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>298000</v>
+      </c>
+      <c r="E21" s="3">
         <v>195900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>90400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>30100</v>
       </c>
-      <c r="G21" s="3">
-        <v>13000</v>
-      </c>
       <c r="H21" s="3">
+        <v>10300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-50000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-23600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-50900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-73100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-64600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-69200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-49900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-20100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>44300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>84000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>105200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>90600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>128300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>158300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>89600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>314100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>159100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>144100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>77200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>111700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>123300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>115200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>35400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-10500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>57400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>78200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>53800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>26500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>119100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>25400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-11100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>-28500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>32800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E22" s="3">
         <v>6200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>9700</v>
       </c>
       <c r="N22" s="3">
         <v>9700</v>
       </c>
       <c r="O22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="P22" s="3">
         <v>9400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>26500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>17100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>16900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>16400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>16300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>15900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>15600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>18300</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>11400</v>
       </c>
       <c r="AE22" s="3">
         <v>11400</v>
       </c>
       <c r="AF22" s="3">
+        <v>11400</v>
+      </c>
+      <c r="AG22" s="3">
         <v>11300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>5100</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>4600</v>
       </c>
       <c r="AJ22" s="3">
         <v>4600</v>
@@ -2399,10 +2439,10 @@
         <v>4600</v>
       </c>
       <c r="AL22" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AM22" s="3">
         <v>4400</v>
-      </c>
-      <c r="AM22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AN22" s="3" t="s">
         <v>17</v>
@@ -2413,252 +2453,261 @@
       <c r="AP22" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="AQ22" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7458300</v>
+      </c>
+      <c r="E23" s="3">
         <v>183800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>96500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-39200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-42300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-79200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-127500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-107400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-101500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-69300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-45400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-48700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-27100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>18800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>37100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>29300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>69100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>99600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>28500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>252900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>98100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>83600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>14600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>48600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>57700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>53400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-21100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-82500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>17700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>52600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>27700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>95500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-27600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>-44400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>17900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-5700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-296600</v>
+      </c>
+      <c r="E24" s="3">
         <v>39600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-224700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>18600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>125000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>19200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>18100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>27400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>14900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>16500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>19200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>8600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-8200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
-      </c>
       <c r="AK24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="3">
         <v>-109300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>27300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>11600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>6100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2779,252 +2828,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-7161700</v>
+      </c>
+      <c r="E26" s="3">
         <v>144200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>78200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>213300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-44100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-60900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-82400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-252500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-127000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-99100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-67900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-60200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-39300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-31700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>34700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>26000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>56700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>81500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>21500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>225500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>83200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>67100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>43400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>49100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>47600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-25800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-74300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>16300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>47400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>31000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>204800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>7100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-54900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>-56000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>11800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7160800</v>
+      </c>
+      <c r="E27" s="3">
         <v>142500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>78200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>213300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-44100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-60900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-82400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-252500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-127000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-99100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-67900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-60200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-39300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-31700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>34700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>26000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>56700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>81500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>21500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>225500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>83200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>67100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>43400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>49100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>47600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-25800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-74300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>16200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>46100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>30000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>199800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>6900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-55200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-56200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>11600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3145,8 +3203,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3225,17 +3286,17 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>17</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>17</v>
@@ -3243,17 +3304,17 @@
       <c r="AH29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-83000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>17</v>
@@ -3267,8 +3328,11 @@
       <c r="AP29" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3389,8 +3453,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3511,252 +3578,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-13800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-8200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-21700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-14700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-11400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>18200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-9300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-5200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>31500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>58000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-4600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>22500</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7161700</v>
+      </c>
+      <c r="E33" s="3">
         <v>144200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>78200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>213300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-44100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-60900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-82400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-252500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-127000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-99100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-67900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-60200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-39300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-31700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>34700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>26000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>56700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>81500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>21500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>225500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>83200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>67100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>43400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>49100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>47600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-25800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-74300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>16200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>46100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>32500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>116800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>6900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-55200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-56200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>11600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3877,257 +3953,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7161700</v>
+      </c>
+      <c r="E35" s="3">
         <v>144200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>78200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>213300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-44100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-60900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-82400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-252500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-127000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-99100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-67900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-60200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-39300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-31700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>34700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>26000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>56700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>81500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>21500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>225500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>83200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>67100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>43400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>49100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>47600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-25800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-74300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>16200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>46100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>32500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>116800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>6900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-55200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-56200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>11600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46018</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44562</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44191</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4170,8 +4255,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4214,243 +4300,247 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2043500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2617800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>657700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>772900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>520700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>516400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>479700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>489200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>436700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>425000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>469300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>861600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>859000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>549200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>592100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>605300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1290200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1130300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>552000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>611000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>774300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>687700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>321300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>269500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>298000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>688300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1085000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>539000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>432600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>357300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>371300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>459400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>397300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>176800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>202100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>150800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>272900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>577900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>155900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>166800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>694900</v>
+      </c>
+      <c r="E42" s="3">
         <v>554500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>497600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>348900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>356400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>350300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>417000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>426900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>450300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>445900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>754700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1082700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1154600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1118000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1088300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1019600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1258800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1433800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1470400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1273600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1171700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1366900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1379000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1341200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1255800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>763100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>230600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>291900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>335900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>340200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>312800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>274900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>314200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>516000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>422400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>381700</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>282400</v>
-      </c>
-      <c r="AN42" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AO42" s="3" t="s">
         <v>17</v>
@@ -4458,263 +4548,272 @@
       <c r="AP42" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="AQ42" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>531400</v>
+      </c>
+      <c r="E43" s="3">
         <v>452500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>383100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>311900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>255200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>260500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>233300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>204300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>200500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>234800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>255500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>228000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>252800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>284600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>330500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>340500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>262000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>242200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>239200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>263200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>212800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>224800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>276700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>263600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>233500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>303100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>343600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>339600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>286200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>329700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>266500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>239600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>197100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>164700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>222100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>173800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>166300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>185400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>192500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>156500</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>691600</v>
+      </c>
+      <c r="E44" s="3">
         <v>632800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>570400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>531600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>470100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>422900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>402300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>403300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>398400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>420700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>471700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>428000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>408600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>410200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>366900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>366200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>250100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>224000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>208100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>207000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>196400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>210700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>207100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>212600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>188900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>172700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>179600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>202200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>228800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>272200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>303200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>136600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>153600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>144200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>147300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>147200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>145200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>116900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>121000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="3">
         <v>49100</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>17</v>
@@ -4722,17 +4821,17 @@
       <c r="H45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="3">
         <v>14000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>7500</v>
       </c>
       <c r="K45" s="3">
         <v>7500</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>17</v>
+      <c r="L45" s="3">
+        <v>7500</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>17</v>
@@ -4746,208 +4845,214 @@
       <c r="P45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R45" s="3">
         <v>114800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>106800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>78100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>70300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>70400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>68200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>81600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>79700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>82100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>79800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>73800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>35800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>44200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>50500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>49300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>118700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>103100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>70600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>65000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>63000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>59900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>69000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>63500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>61400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>58200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>62300</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4161900</v>
+      </c>
+      <c r="E46" s="3">
         <v>4395700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2283200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2085600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1717300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1667300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1651400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1636200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1590100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1650000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2062100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2691700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2777900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2463600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2492600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2438400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3139200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3100600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2540100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2423000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2436800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2569800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2266200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2166700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2050000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1963000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1883000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1423200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1332800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1418100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1356900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1181100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1127200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1064700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1053800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>922500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>930300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>941600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>527600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>489300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4990,8 +5095,8 @@
       <c r="P47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5068,252 +5173,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1188300</v>
+      </c>
+      <c r="E48" s="3">
         <v>991300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>843100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>825300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>754300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>725500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>696300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>674100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>645300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>655400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>663600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>580400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>566800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>564400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>572600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>567400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>434100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>430700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>434700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>428400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>428500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>448300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>457600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>468100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>471700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>491800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>505700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>524900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>433300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>390600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>444700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>318600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>280600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>264500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>301300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>293700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>273500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>246600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>219600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>196000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1396200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1429200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1457600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1491600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1526000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1560700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1595800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1634800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1673300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1744400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1785200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1130300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1154300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1194600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1238100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1269700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>524600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>545800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>567200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>588700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>610100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>632100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>654100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>665000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>685700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>706900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>726900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>745500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>764300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>772100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>789700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>17600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>44600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>57200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>20400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>21000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>21500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>22300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>16000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5434,8 +5548,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5556,130 +5673,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E52" s="3">
         <v>11500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>114800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>111900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>64300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>56400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>73700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>78900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>76200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>95700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>90300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>87600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>85200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>107000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>105600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>174200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>186200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>190600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>205300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>127700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>129100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>131800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>131900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>11200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>7600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>34000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>33500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>34100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5800,130 +5923,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7307500</v>
+      </c>
+      <c r="E54" s="3">
         <v>7027900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4805300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4613100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4218700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3975000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3966100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3969600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3931900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4204500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4656000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4545000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4632100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4354000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4418100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4387400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4162200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4133500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3615700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3519000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3551600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3745900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3468200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3387400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3292600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3268700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3221200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2867800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2716600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2771400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2796600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1645000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1581500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1518200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1507400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1248400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1232900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1244500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>796700</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>737500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5966,8 +6095,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6010,240 +6140,244 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>567400</v>
+      </c>
+      <c r="E57" s="3">
         <v>392700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>347400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>278600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>225200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>195200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>184700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>163100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>126300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>133400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>163000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>134600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>169400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>198700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>205600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>205700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>156700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>126800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>118200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>101600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>116900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>104700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>111300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>146000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>150800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>144600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>143700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>152200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>160800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>204100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>199200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>127600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>126500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>100900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>113000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>111600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>114800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>118400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>127800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>108300</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1610400</v>
+      </c>
+      <c r="E58" s="3">
         <v>3251100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3252900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1091200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>21000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>22700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>334200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>327500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>326000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>440600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>420700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>420200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>409900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>406100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>401000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>395800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>390700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>385400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>380600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>15900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>5400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>5800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>8700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>5400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>7300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>9200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>9100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>4900</v>
-      </c>
-      <c r="AM58" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="AN58" s="3" t="s">
         <v>17</v>
@@ -6254,496 +6388,511 @@
       <c r="AP58" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="AQ58" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>91500</v>
+      </c>
+      <c r="E59" s="3">
         <v>62900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>41600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>53100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>49900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>54900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>52900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>56400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>68300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>45000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>31300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>55600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>36800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>188000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>176900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>149900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>127800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>137500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>114300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>157000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>184100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>155400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>147000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>131600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>138200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>153400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>148700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>127800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>148100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>117600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>80900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>80200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>81400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>95600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>60700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>69400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>73700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>74200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>55200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2480500</v>
+      </c>
+      <c r="E60" s="3">
         <v>3865300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3767600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1526200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>392800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>353000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>346900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>305100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>269300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>317600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>658400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>593700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>633800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>768900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>814300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>802800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>716500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>660700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>656700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>611700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>664600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>674200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>647300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>293400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>283000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>286700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>304200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>316800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>294000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>358000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>325500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>213900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>214000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>191500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>217700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>177200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>184200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>192100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>202000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>163500</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E61" s="3">
         <v>62600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>69800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2189000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2586200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2588200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2587300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2599000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2546200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2549700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2554600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2542100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2547700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1953900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1900300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1899500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1466100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1447600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>810300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>800000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>789800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>778900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>769100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1134700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1120300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1106100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1092200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>840000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>835900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>832400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>829200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>338500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>334600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>330700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>328800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>324000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>317500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>313400</v>
       </c>
-      <c r="AO61" s="3">
-        <v>0</v>
-      </c>
       <c r="AP61" s="3">
         <v>0</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>108000</v>
+      </c>
+      <c r="E62" s="3">
         <v>109800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>104500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>100600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>88100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>108000</v>
       </c>
       <c r="I62" s="3">
         <v>108000</v>
       </c>
       <c r="J62" s="3">
+        <v>108000</v>
+      </c>
+      <c r="K62" s="3">
         <v>107600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>95900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>89200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>86200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>75600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>81800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>66000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>159900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>158700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>104600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>113100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>126800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>135900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>124400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>127800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>129900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>143200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>140100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>141700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>143200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>149700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>89600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>77100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>82200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>73300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>71000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>83600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>60800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>70300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>76600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>234600</v>
-      </c>
-      <c r="AO62" s="3">
-        <v>42500</v>
       </c>
       <c r="AP62" s="3">
         <v>42500</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>42500</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6864,8 +7013,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6986,8 +7138,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7108,130 +7263,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2663600</v>
+      </c>
+      <c r="E66" s="3">
         <v>4054500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3958700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3832300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3084000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3095500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3093800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3073700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2974600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3027800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3378200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3234200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3276300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2816000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2874500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2861000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2287200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2221400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1593800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1547600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1578800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1580900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1546300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1571300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1543400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1534500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1539600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1306500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1219500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1267500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1236900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>661500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>655400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>641600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>643100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>607300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>614100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>775900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>280300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>241800</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7274,8 +7435,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7396,8 +7558,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7518,8 +7683,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7640,8 +7808,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7762,130 +7933,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-7796300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-634600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-778800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-857000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-861200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1074500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1030400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-969500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-887100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-634600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-507600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-408500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-340600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-140600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-101300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-69600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-129100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-60500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>237500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>210700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>220900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>440400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>214900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>131700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>64600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>69200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>25800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>176700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>129100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>154900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>229200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>213000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>166400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>133200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>130700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-73900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-83200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-28000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>28200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>16600</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8006,8 +8183,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8128,8 +8308,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8250,130 +8433,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4643900</v>
+      </c>
+      <c r="E76" s="3">
         <v>2973400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>846600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>780800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1134700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>879500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>872300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>895900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>957300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1176700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1277800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1310800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1355800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1538000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1543600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1526400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1875000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1912100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2021900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1971400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1972800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2165000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1921900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1816100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1749200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1734200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1681600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1561300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1497100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1503900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1559700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>983500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>926100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>876600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>864300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>641100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>618800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>468600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>516400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>495700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8494,257 +8683,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46018</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44562</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44191</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7161700</v>
+      </c>
+      <c r="E81" s="3">
         <v>144200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>78200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>213300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-44100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-60900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-82400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-252500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-127000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-99100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-67900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-60200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-39300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-31700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>34700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>26000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>56700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>81500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>21500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>225500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>83200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>67100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>43400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>49100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>47600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-25800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-74300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>16200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>46100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>32500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>116800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>6900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-55200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-56200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>11600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8787,130 +8985,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E83" s="3">
         <v>25000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>27000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>28200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>27000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>27200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>28200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>28000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>27700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>62500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>56700</v>
-      </c>
-      <c r="S83" s="3">
-        <v>41600</v>
       </c>
       <c r="T83" s="3">
         <v>41600</v>
       </c>
       <c r="U83" s="3">
+        <v>41600</v>
+      </c>
+      <c r="V83" s="3">
         <v>42100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>41800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>43100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>44800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>44700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>44500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>46700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>47500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>47300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>50400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>45100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>60700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>31200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>20500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>21500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>19200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>19000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>17500</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>16500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>15900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>14900</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9031,8 +9233,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9153,8 +9358,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9275,8 +9483,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9397,8 +9608,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9519,130 +9733,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>363000</v>
+      </c>
+      <c r="E89" s="3">
         <v>203800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>126700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>57900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>64000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>24300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>39600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>35500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>49200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>94900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>20800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>114300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>76600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>206500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>61900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>124200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>381300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>128500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>104700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>122700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>151800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>162300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>87500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>127700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>42800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>102400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>57200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>37600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>95100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>105100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>9700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>13100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>16400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>19200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>36300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9685,130 +9905,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-166800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-124700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-83600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-76200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-53900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-62800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-40200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-74100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-24600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-31000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-57800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-36300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-29400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-39900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-22900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-28600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-18600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-26100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-17900</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>16300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-26300</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-600</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-20300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-22700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-17200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-38100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-35700</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-35400</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-28900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9929,8 +10153,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10051,130 +10278,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-304400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-181900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-231400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-67800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-59400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>53100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-30700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-47100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>290300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-394900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>17800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-70900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-52000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-104500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-646600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>142700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-228900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-116900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>197300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-75000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-114000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-509800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-535700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>36100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>21700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-54400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-52900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-681900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>9500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>181700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-117600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-58600</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-132500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-320600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-40800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-35400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-28900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10217,8 +10450,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10261,8 +10495,8 @@
       <c r="P96" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10339,8 +10573,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10461,8 +10698,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10583,8 +10823,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10705,130 +10948,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-632900</v>
+      </c>
+      <c r="E100" s="3">
         <v>1938200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>262100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>60000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-327600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>4100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>331500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-59100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-97100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>524900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-36600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-108300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-234900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-19200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-12300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>347600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>491600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>4400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>2000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>445700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>6700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10871,8 +11120,8 @@
       <c r="P101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10920,155 +11169,161 @@
         <v>0</v>
       </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-200</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="AL101" s="3">
         <v>400</v>
       </c>
       <c r="AM101" s="3">
+        <v>400</v>
+      </c>
+      <c r="AN101" s="3">
         <v>500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-574300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1960100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-115200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>252200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>36700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-9500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>52500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>11700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-44300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-392300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>309800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-42900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-684900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>159900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>578300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-59000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-163300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>86600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>366400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>51800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-28500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-390800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-396200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>546000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>106400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>74300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-13000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-88100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>62100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>220500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-25300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>51300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-122100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-305000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>422000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-10900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>9700</v>
       </c>
     </row>
